--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_valparaiso.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:05</t>
+    <t xml:space="preserve">2026-09-24 00:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -570,7 +570,7 @@
         <v>-0.06</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>-0.02</v>
@@ -616,7 +616,7 @@
         <v>0.15</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0.21</v>
@@ -685,10 +685,10 @@
         <v>0.01</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="8">
@@ -708,10 +708,10 @@
         <v>0.12</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="9">
@@ -731,10 +731,10 @@
         <v>0.2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -757,7 +757,7 @@
         <v>0.16</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="11">
@@ -800,10 +800,10 @@
         <v>0.08</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="13">
@@ -823,7 +823,7 @@
         <v>0.25</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0.12</v>
@@ -846,10 +846,10 @@
         <v>-0.43</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="15">
@@ -869,7 +869,7 @@
         <v>-0.21</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>-0.22</v>
@@ -892,10 +892,10 @@
         <v>-0.41</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="17">
@@ -961,10 +961,10 @@
         <v>0.3</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="20">
@@ -984,10 +984,10 @@
         <v>0.39</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="21">
@@ -1145,10 +1145,10 @@
         <v>-0.19</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="28">
@@ -1168,10 +1168,10 @@
         <v>0.09</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="29">
@@ -1191,7 +1191,7 @@
         <v>0.07</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>0.14</v>
@@ -1260,10 +1260,10 @@
         <v>-0.52</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-0.76</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="33">
@@ -1352,7 +1352,7 @@
         <v>-0.09</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>-0.07</v>
@@ -1421,10 +1421,10 @@
         <v>0.48</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="40">
@@ -1444,10 +1444,10 @@
         <v>0.41</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="41">
@@ -1884,7 +1884,7 @@
         <v>0.08</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="60">
@@ -1907,7 +1907,7 @@
         <v>0.13</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="61">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_valparaiso.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:56</t>
+    <t xml:space="preserve">2026-10-01 23:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2019_valparaiso.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:21</t>
+    <t xml:space="preserve">2026-10-05 19:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
